--- a/mappingCorps/ig/FRObservationVitalSignsLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRObservationVitalSignsLMCDAFHIR.xlsx
@@ -40,7 +40,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping Métier/CDA/FHIR : "Signe vital observé"</t>
+    <t>Mapping Métier/CDA/FHIR : "Observation Vital Sign"</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMSigneVitalObserve vers le profil CDA FRCDASigneVitalObserve, puis vers le profil FHIR FRObservationVitalSignsDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMObservationVitalSign vers le profil CDA FRCDASigneVitalObserve, puis vers le profil FHIR FRObservationVitalSignsDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-signe-vital-observe</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation-vital-sign</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-signe-vital-observe</t>
   </si>
   <si>
-    <t>FRLMSigneVitalObserve</t>
+    <t>FRLMObservationVitalSign</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,61 +118,61 @@
     <t>FRCDASigneVitalObserve</t>
   </si>
   <si>
-    <t>FRLMSigneVitalObserve.identifiant</t>
+    <t>FRLMObservationVitalSign.header.identifier</t>
   </si>
   <si>
     <t>FRCDASigneVitalObserve.id</t>
   </si>
   <si>
-    <t>FRLMSigneVitalObserve.code</t>
+    <t>FRLMObservationVitalSign.observationDate[x]</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.type</t>
   </si>
   <si>
     <t>FRCDASigneVitalObserve.code</t>
   </si>
   <si>
-    <t>FRLMSigneVitalObserve.description</t>
+    <t>FRLMObservationVitalSign.header.status</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.method</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.methodCode</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.targetSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.result</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.value</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.interpretation</t>
+  </si>
+  <si>
+    <t>FRCDASigneVitalObserve.interpretationCode</t>
+  </si>
+  <si>
+    <t>FRLMObservationVitalSign.note</t>
   </si>
   <si>
     <t>FRCDASigneVitalObserve.text</t>
   </si>
   <si>
-    <t>FRLMSigneVitalObserve.statut</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.date</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.observationEffectuee</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.value</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.interpretation</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.interpretationCode</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.methodeUtilisee</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.methodCode</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.siteObservation</t>
-  </si>
-  <si>
-    <t>FRCDASigneVitalObserve.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMSigneVitalObserve.auteur</t>
+    <t>FRLMObservationVitalSign.header.author</t>
   </si>
   <si>
     <t>FRCDASigneVitalObserve.author</t>
@@ -187,16 +187,19 @@
     <t>FRObservationVitalSignsDocument.identifier</t>
   </si>
   <si>
+    <t>FRObservationVitalSignsDocument.effectiveDateTime</t>
+  </si>
+  <si>
     <t>FRObservationVitalSignsDocument.code</t>
   </si>
   <si>
-    <t>FRObservationVitalSignsDocument.code.text</t>
-  </si>
-  <si>
     <t>FRObservationVitalSignsDocument.status</t>
   </si>
   <si>
-    <t>FRObservationVitalSignsDocument.effectiveDateTime</t>
+    <t>FRObservationVitalSignsDocument.method</t>
+  </si>
+  <si>
+    <t>FRObservationVitalSignsDocument.bodySite</t>
   </si>
   <si>
     <t>FRObservationVitalSignsDocument.component.valueQuantity</t>
@@ -205,13 +208,10 @@
     <t>FRObservationVitalSignsDocument.interpretation</t>
   </si>
   <si>
-    <t>FRObservationVitalSignsDocument.method</t>
-  </si>
-  <si>
-    <t>FRObservationVitalSignsDocument.bodySite</t>
-  </si>
-  <si>
-    <t>FRObservationVitalSignsDocument.performer.extension:author</t>
+    <t>FRObservationVitalSignsDocument.note</t>
+  </si>
+  <si>
+    <t>FRObservationVitalSignsDocument.extension:author</t>
   </si>
 </sst>
 </file>
@@ -672,7 +672,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -702,7 +702,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -715,7 +715,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -728,7 +728,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -741,7 +741,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -754,7 +754,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -767,7 +767,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -780,7 +780,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -793,7 +793,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -806,7 +806,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -819,7 +819,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
